--- a/students.xlsx
+++ b/students.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/varunbhadurgattenagaraj/Downloads/HR-CheckIn-Morning/HR-Check-In/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71ECDFF-85AC-0B40-B560-4E067B5B65E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Student</t>
   </si>
@@ -203,26 +212,49 @@
   </si>
   <si>
     <t>Bezan Viccaji</t>
+  </si>
+  <si>
+    <t>Emili Kosik</t>
+  </si>
+  <si>
+    <t>Elizabeth Muller</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -231,42 +263,46 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -456,22 +492,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="38.25"/>
-    <col customWidth="1" min="2" max="2" width="44.88"/>
+    <col min="1" max="1" width="38.1640625" customWidth="1"/>
+    <col min="2" max="2" width="44.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -479,506 +518,521 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>305537.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+        <v>305537</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>126996.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+        <v>126996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>111841.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+        <v>111841</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>150247.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+        <v>150247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>309234.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+        <v>309234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>321078.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+        <v>321078</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>137937.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+        <v>137937</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="2">
-        <v>310889.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
+        <v>310889</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>124129.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+        <v>124129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>188142.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
+        <v>188142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="2">
-        <v>126788.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+        <v>126788</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="2">
-        <v>188370.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+        <v>188370</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>306636.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
+        <v>306636</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>207911.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
+        <v>207911</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>136288.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
+        <v>136288</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>138332.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
+        <v>138332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>302242.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
+        <v>302242</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>137278.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+        <v>137278</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="2">
-        <v>180507.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
+        <v>180507</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="2">
-        <v>137323.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
+        <v>137323</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="2">
-        <v>138524.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
+        <v>138524</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>147201.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
+        <v>147201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="2">
-        <v>137923.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
+        <v>137923</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="2">
-        <v>144991.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
+        <v>144991</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>307150.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="s">
+        <v>307150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>147134.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
+        <v>147134</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>301460.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
+        <v>301460</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>185941.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
+        <v>185941</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>152156.0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="s">
+        <v>152156</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>310376.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="s">
+        <v>310376</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>124261.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="s">
+        <v>124261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B33" s="2">
-        <v>167703.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
+        <v>167703</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B34" s="2">
-        <v>306601.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
+        <v>306601</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B35" s="2">
-        <v>185963.0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
+        <v>185963</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B36" s="2">
-        <v>139987.0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
+        <v>139987</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B37" s="2">
-        <v>118221.0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
+        <v>118221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>156038.0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
+        <v>156038</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>134986.0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
+        <v>134986</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>126951.0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="s">
+        <v>126951</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>119530.0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
+        <v>119530</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>318759.0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
+        <v>318759</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>137276.0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="s">
+        <v>137276</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>138283.0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="s">
+        <v>138283</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>319657.0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="s">
+        <v>319657</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>137405.0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="s">
+        <v>137405</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>124446.0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="s">
+        <v>124446</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B48" s="2">
-        <v>151579.0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="s">
+        <v>151579</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>119022.0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="s">
+        <v>119022</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>309213.0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="s">
+        <v>309213</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B51" s="2">
-        <v>126807.0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="s">
+        <v>126807</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A52" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B52" s="2">
-        <v>125718.0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="s">
+        <v>125718</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B53" s="2">
-        <v>303146.0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="s">
+        <v>303146</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="2">
-        <v>152846.0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="s">
+        <v>152846</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A55" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B55" s="2">
-        <v>324170.0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="s">
+        <v>324170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B56" s="2">
-        <v>155576.0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="s">
+        <v>155576</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A57" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B57" s="2">
-        <v>136010.0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="s">
+        <v>136010</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A58" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B58" s="2">
-        <v>311947.0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="s">
+        <v>311947</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A59" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B59" s="2">
-        <v>139680.0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="s">
+        <v>139680</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A60" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B60" s="2">
-        <v>154554.0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
+        <v>154554</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A61" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B61" s="2">
-        <v>305884.0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="s">
+        <v>305884</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A62" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B62" s="2">
-        <v>187406.0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
+        <v>187406</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="13" x14ac:dyDescent="0.15">
+      <c r="A63" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B63" s="2">
-        <v>309543.0</v>
+        <v>309543</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64">
+        <v>212802</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65" s="4">
+        <v>680869</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>